--- a/excel_upload_masters/templates/06_candidates.xlsx
+++ b/excel_upload_masters/templates/06_candidates.xlsx
@@ -4,10 +4,11 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="candidates" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="lists" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="candidates" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,6 +433,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Yet to join</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Met</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Joined</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Not met</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Accepted</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PIPELINE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No show</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Declined</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ON HOLD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>UNPROCESSED</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CANCELLED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:BO2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -836,7 +958,11 @@
           <t>Date/datetime — ISO-8601 or Excel date</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>Date/datetime — ISO-8601 or Excel date</t>
@@ -869,7 +995,11 @@
           <t>JSON.</t>
         </is>
       </c>
-      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>JSON.</t>
@@ -882,10 +1012,26 @@
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>Pick from list (dropdown)</t>
+        </is>
+      </c>
       <c r="AU2" s="2" t="inlineStr"/>
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" s="2" t="inlineStr"/>
@@ -933,6 +1079,26 @@
       <c r="BO2" s="2" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="6">
+    <dataValidation sqref="AC3:AC5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$A$1:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AL3:AL5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$B$1:$B$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AQ3:AQ5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$C$1:$C$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AR3:AR5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$D$1:$D$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AS3:AS5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$D$1:$D$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AT3:AT5002" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Choose a value from the list, or clear the cell." type="list">
+      <formula1>=lists!$D$1:$D$4</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>